--- a/tests/reference_data/test_scenario_fms_unconstrained_abs.xlsx
+++ b/tests/reference_data/test_scenario_fms_unconstrained_abs.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BAF16E-C11A-4757-962B-74A1E5E78031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6105" yWindow="2445" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-25920" yWindow="1965" windowWidth="21600" windowHeight="11295" activeTab="5" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
@@ -930,37 +930,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFCC0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -2012,42 +1982,42 @@
   </sheetData>
   <autoFilter ref="B6:E6" xr:uid="{89FFA668-DA1A-459B-BD42-D0D7F7709F0D}"/>
   <conditionalFormatting sqref="C15:C16">
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" operator="notEqual">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C21:C22">
-    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="notEqual">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="notEqual">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C29">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="notEqual">
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C37:C38">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="notEqual">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3409,10 +3379,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:K6">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="notEqual">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3691,15 +3661,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Asiakirja" ma:contentTypeID="0x010100806C55B750152A459818B636E97A41C3" ma:contentTypeVersion="19" ma:contentTypeDescription="Luo uusi asiakirja." ma:contentTypeScope="" ma:versionID="74fd9cb75cef04cf26a1ff9ddef01b4b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xmlns:ns3="145cc194-9bea-4db6-b116-a042a4529fcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="afbcbfdd38894bc2ff0644b00c8ec680" ns2:_="" ns3:_="">
     <xsd:import namespace="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
@@ -3962,6 +3923,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
   <ds:schemaRefs>
@@ -3980,14 +3950,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60021C7-CA75-4673-96EA-55284BF81134}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4004,4 +3966,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>